--- a/output/pdf_financials_xlsx/MONI.xlsx
+++ b/output/pdf_financials_xlsx/MONI.xlsx
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.930354</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.07543</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.037441</v>
+        <v>1.023414</v>
       </c>
     </row>
     <row r="11">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.930354</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.07543</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.037441</v>
+        <v>-1.023414</v>
       </c>
     </row>
     <row r="12">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003954</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000929</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.9264</v>
+        <v>-0.930354</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.074502</v>
+        <v>-0.075431</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.023414</v>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.9264</v>
+        <v>-0.930354</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.074502</v>
+        <v>-0.075431</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.023414</v>
@@ -1259,16 +1259,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.014937</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.197843</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.08613999999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.138422</v>
       </c>
     </row>
     <row r="35">
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.014937</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.197843</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.08613999999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.138422</v>
       </c>
     </row>
     <row r="37">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.930354</v>
+        <v>0.930354</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>-0.07543</v>
+        <v>0.07543</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7889,11 +7889,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>-1.078507</v>
+        <v>1.078507</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
